--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5.567736669158903</v>
+        <v>0.9047572087383219</v>
       </c>
       <c r="D2" t="n">
-        <v>7.143583953290466</v>
+        <v>1.160832392409701</v>
       </c>
       <c r="E2" t="n">
-        <v>13.5353870694113</v>
+        <v>2.199500398779337</v>
       </c>
       <c r="F2" t="n">
-        <v>9.536610446511952</v>
+        <v>1.549699197558192</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.96916143124672</v>
+        <v>5.032488732577592</v>
       </c>
       <c r="D3" t="n">
-        <v>32.9953724738121</v>
+        <v>5.361748026994466</v>
       </c>
       <c r="E3" t="n">
-        <v>13.5353870694113</v>
+        <v>2.199500398779337</v>
       </c>
       <c r="F3" t="n">
-        <v>9.536610446511952</v>
+        <v>1.549699197558192</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.60416088027448</v>
+        <v>4.160676143044603</v>
       </c>
       <c r="D4" t="n">
-        <v>21.83148191586414</v>
+        <v>3.547615811327923</v>
       </c>
       <c r="E4" t="n">
-        <v>13.5353870694113</v>
+        <v>2.199500398779337</v>
       </c>
       <c r="F4" t="n">
-        <v>9.536610446511952</v>
+        <v>1.549699197558192</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.59919709336725</v>
+        <v>7.734869527672179</v>
       </c>
       <c r="D5" t="n">
-        <v>23.77011169525904</v>
+        <v>3.862643150479594</v>
       </c>
       <c r="E5" t="n">
-        <v>13.5353870694113</v>
+        <v>2.199500398779337</v>
       </c>
       <c r="F5" t="n">
-        <v>9.536610446511952</v>
+        <v>1.549699197558192</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.42215459224755</v>
+        <v>5.918600121240227</v>
       </c>
       <c r="D6" t="n">
-        <v>25.39094032764801</v>
+        <v>4.126027803242803</v>
       </c>
       <c r="E6" t="n">
-        <v>13.5353870694113</v>
+        <v>2.199500398779337</v>
       </c>
       <c r="F6" t="n">
-        <v>9.536610446511952</v>
+        <v>1.549699197558192</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.70753996821236</v>
+        <v>3.039975244834508</v>
       </c>
       <c r="D7" t="n">
-        <v>19.31993188895873</v>
+        <v>3.139488931955793</v>
       </c>
       <c r="E7" t="n">
-        <v>13.5353870694113</v>
+        <v>2.199500398779337</v>
       </c>
       <c r="F7" t="n">
-        <v>9.536610446511952</v>
+        <v>1.549699197558192</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.63842809095637</v>
+        <v>6.766244564780409</v>
       </c>
       <c r="D8" t="n">
-        <v>43.52853353581037</v>
+        <v>7.073386699569185</v>
       </c>
       <c r="E8" t="n">
-        <v>13.5353870694113</v>
+        <v>2.199500398779337</v>
       </c>
       <c r="F8" t="n">
-        <v>9.536610446511952</v>
+        <v>1.549699197558192</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>62.92478372939931</v>
+        <v>10.22527735602739</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72976170376604</v>
+        <v>5.156086276861982</v>
       </c>
       <c r="E9" t="n">
-        <v>13.5353870694113</v>
+        <v>2.199500398779337</v>
       </c>
       <c r="F9" t="n">
-        <v>9.536610446511952</v>
+        <v>1.549699197558192</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>23.96355250890469</v>
+        <v>3.894077282697013</v>
       </c>
       <c r="D10" t="n">
-        <v>25.34261992293403</v>
+        <v>4.118175737476781</v>
       </c>
       <c r="E10" t="n">
-        <v>13.5353870694113</v>
+        <v>2.199500398779337</v>
       </c>
       <c r="F10" t="n">
-        <v>9.536610446511952</v>
+        <v>1.549699197558192</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>45.6283178827637</v>
+        <v>7.414601655949102</v>
       </c>
       <c r="D11" t="n">
-        <v>35.93997982669594</v>
+        <v>5.84024672183809</v>
       </c>
       <c r="E11" t="n">
-        <v>13.5353870694113</v>
+        <v>2.199500398779337</v>
       </c>
       <c r="F11" t="n">
-        <v>9.536610446511952</v>
+        <v>1.549699197558192</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>34.34012163960838</v>
+        <v>5.580269766436363</v>
       </c>
       <c r="D12" t="n">
-        <v>36.02626106747406</v>
+        <v>5.854267423464535</v>
       </c>
       <c r="E12" t="n">
-        <v>13.5353870694113</v>
+        <v>2.199500398779337</v>
       </c>
       <c r="F12" t="n">
-        <v>9.536610446511952</v>
+        <v>1.549699197558192</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.77997729523508</v>
+        <v>5.3267463104757</v>
       </c>
       <c r="D13" t="n">
-        <v>31.70654618930143</v>
+        <v>5.152313755761482</v>
       </c>
       <c r="E13" t="n">
-        <v>13.5353870694113</v>
+        <v>2.199500398779337</v>
       </c>
       <c r="F13" t="n">
-        <v>9.536610446511952</v>
+        <v>1.549699197558192</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>43.07307323518111</v>
+        <v>6.999374400716931</v>
       </c>
       <c r="D14" t="n">
-        <v>44.71392872284711</v>
+        <v>7.266013417462656</v>
       </c>
       <c r="E14" t="n">
-        <v>13.5353870694113</v>
+        <v>2.199500398779337</v>
       </c>
       <c r="F14" t="n">
-        <v>9.536610446511952</v>
+        <v>1.549699197558192</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>37.95108968032018</v>
+        <v>6.167052073052029</v>
       </c>
       <c r="D15" t="n">
-        <v>25.53918557824427</v>
+        <v>4.150117656464694</v>
       </c>
       <c r="E15" t="n">
-        <v>13.5353870694113</v>
+        <v>2.199500398779337</v>
       </c>
       <c r="F15" t="n">
-        <v>9.536610446511952</v>
+        <v>1.549699197558192</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>60.25851923353846</v>
+        <v>9.79200937545</v>
       </c>
       <c r="D16" t="n">
-        <v>26.24880949681338</v>
+        <v>4.265431543232173</v>
       </c>
       <c r="E16" t="n">
-        <v>13.5353870694113</v>
+        <v>2.199500398779337</v>
       </c>
       <c r="F16" t="n">
-        <v>9.536610446511952</v>
+        <v>1.549699197558192</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>37.3837127594859</v>
+        <v>6.074853323416459</v>
       </c>
       <c r="D17" t="n">
-        <v>28.27090839803769</v>
+        <v>4.594022614681125</v>
       </c>
       <c r="E17" t="n">
-        <v>13.5353870694113</v>
+        <v>2.199500398779337</v>
       </c>
       <c r="F17" t="n">
-        <v>9.536610446511952</v>
+        <v>1.549699197558192</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>48.04885855667641</v>
+        <v>7.807939515459918</v>
       </c>
       <c r="D18" t="n">
-        <v>9.701932499450951</v>
+        <v>1.57656403116078</v>
       </c>
       <c r="E18" t="n">
-        <v>13.5353870694113</v>
+        <v>2.199500398779337</v>
       </c>
       <c r="F18" t="n">
-        <v>9.536610446511952</v>
+        <v>1.549699197558192</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31.29602431989921</v>
+        <v>5.085603951983622</v>
       </c>
       <c r="D19" t="n">
-        <v>31.59145602493912</v>
+        <v>5.133611604052608</v>
       </c>
       <c r="E19" t="n">
-        <v>13.5353870694113</v>
+        <v>2.199500398779337</v>
       </c>
       <c r="F19" t="n">
-        <v>9.536610446511952</v>
+        <v>1.549699197558192</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
